--- a/data/trans_orig/IP18A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37476</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30527</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45759</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95748</t>
+          <t>93891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48173</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64238</t>
+          <t>64585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>61877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>77627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113647</t>
+          <t>115504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136657</t>
+          <t>138611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129587</t>
+          <t>129425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152896</t>
+          <t>153452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145977</t>
+          <t>146092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168294</t>
+          <t>169538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282614</t>
+          <t>281747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313868</t>
+          <t>316254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78690</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65108</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>87310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151121</t>
+          <t>148735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182375</t>
+          <t>183242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61742</t>
+          <t>61399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>77116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74786</t>
+          <t>75105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90391</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142775</t>
+          <t>140972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162818</t>
+          <t>163016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44288</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58883</t>
+          <t>58685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78926</t>
+          <t>80729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109487</t>
+          <t>110175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127102</t>
+          <t>128192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113986</t>
+          <t>113390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133130</t>
+          <t>131683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228120</t>
+          <t>228799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253309</t>
+          <t>254352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49200</t>
+          <t>48512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34130</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72638</t>
+          <t>71595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>356422</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>394946</t>
+          <t>395617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>380118</t>
+          <t>382268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>422228</t>
+          <t>419985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>750925</t>
+          <t>748592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>804747</t>
+          <t>803506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203072</t>
+          <t>202401</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241596</t>
+          <t>240623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201786</t>
+          <t>204029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>243896</t>
+          <t>241746</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417285</t>
+          <t>418526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>471107</t>
+          <t>473440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57029</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76821</t>
+          <t>75219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>57973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77606</t>
+          <t>78188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>119785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147112</t>
+          <t>147999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64741</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84533</t>
+          <t>86037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64842</t>
+          <t>64260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85670</t>
+          <t>84475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136898</t>
+          <t>136011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165313</t>
+          <t>164225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130987</t>
+          <t>132031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154947</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159553</t>
+          <t>159635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184919</t>
+          <t>184969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300507</t>
+          <t>300926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335463</t>
+          <t>334526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>65890</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90943</t>
+          <t>89899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>70187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95603</t>
+          <t>95521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141623</t>
+          <t>142560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176579</t>
+          <t>176160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>98171</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115832</t>
+          <t>116240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101383</t>
+          <t>100789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119463</t>
+          <t>118990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204631</t>
+          <t>204080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231178</t>
+          <t>230434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53641</t>
+          <t>52959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49799</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71134</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97681</t>
+          <t>98232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109127</t>
+          <t>109562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126412</t>
+          <t>126732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106658</t>
+          <t>107669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222606</t>
+          <t>222736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247671</t>
+          <t>248921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56789</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69173</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94238</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>413497</t>
+          <t>415593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>454263</t>
+          <t>454096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>447890</t>
+          <t>446708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>490760</t>
+          <t>490247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>875216</t>
+          <t>874944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>931656</t>
+          <t>933318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213756</t>
+          <t>213923</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>254522</t>
+          <t>252426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>221472</t>
+          <t>221985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264342</t>
+          <t>265524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448595</t>
+          <t>446933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505035</t>
+          <t>505307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39447</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56140</t>
+          <t>56088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34903</t>
+          <t>34091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79121</t>
+          <t>79249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103092</t>
+          <t>103290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>70921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87562</t>
+          <t>87849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67285</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83491</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142311</t>
+          <t>142113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166282</t>
+          <t>166154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125834</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146617</t>
+          <t>146448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147465</t>
+          <t>145678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171498</t>
+          <t>169789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278446</t>
+          <t>280622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>311493</t>
+          <t>310777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48602</t>
+          <t>48771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69385</t>
+          <t>68988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>65366</t>
+          <t>67075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120590</t>
+          <t>121306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153637</t>
+          <t>151461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112775</t>
+          <t>111695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131654</t>
+          <t>130249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>116258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135295</t>
+          <t>135397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232715</t>
+          <t>234883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260507</t>
+          <t>260646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39584</t>
+          <t>40989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>59543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79174</t>
+          <t>79035</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106966</t>
+          <t>104798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105413</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>123021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>98593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116889</t>
+          <t>117193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208519</t>
+          <t>208804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234447</t>
+          <t>235443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48991</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67563</t>
+          <t>66567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93491</t>
+          <t>93206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>401597</t>
+          <t>402102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>441011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415013</t>
+          <t>415971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>455541</t>
+          <t>454660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>827832</t>
+          <t>828723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>884042</t>
+          <t>884751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245680</t>
+          <t>245175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216360</t>
+          <t>217241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256888</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435136</t>
+          <t>434427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>491346</t>
+          <t>490455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26553</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30872</t>
+          <t>30778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55802</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26210</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,47 +7310,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>70,67%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>91,71%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>55153</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>48457</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>60443</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>80,91%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>71,09%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>55153</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>48367</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>60235</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>80,91%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,47 +7423,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>13014</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>7724</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>19710</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>28,91%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>13014</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>7932</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>19800</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22462</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>29373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38259</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>48055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>83614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111564</t>
+          <t>111974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170762</t>
+          <t>170971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191593</t>
+          <t>192659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40313</t>
+          <t>39247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A03-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37567</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30496</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46270</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45537</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37129</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53614</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53816</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>37567</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>30054</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45804</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70784</t>
+          <t>71465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>96139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70114</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61411</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77185</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56177</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48100</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64585</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47898</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63912</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>55,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70114</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61877</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77627</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115504</t>
+          <t>113256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138611</t>
+          <t>137930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>157786</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146311</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>168636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>141724</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>129425</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>153452</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>129957</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>153710</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>61,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>157786</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>146092</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>169538</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281747</t>
+          <t>281637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316254</t>
+          <t>314377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75616</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64766</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87091</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>89862</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78134</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102161</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77876</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>101629</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>38,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>75616</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>63864</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87310</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148735</t>
+          <t>150612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183242</t>
+          <t>183352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83002</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74860</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90225</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69555</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61399</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77116</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61291</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76686</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>83002</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75105</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90693</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140972</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163016</t>
+          <t>162446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32669</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40811</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36475</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28914</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44631</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29344</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>44739</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32669</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24978</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>40566</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58685</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80729</t>
+          <t>80758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>123247</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>113559</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>131973</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>118769</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>110175</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128192</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>109645</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>127423</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>74,85%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>123247</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>113390</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>131683</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>228799</t>
+          <t>229594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254352</t>
+          <t>253304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35287</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39918</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30495</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48512</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31264</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49042</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,15%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44013</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35577</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>53870</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71595</t>
+          <t>72643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97148</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>381638</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>420087</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>357395</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>395617</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>355869</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>393637</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>382268</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>419985</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>748592</t>
+          <t>750086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>803506</t>
+          <t>804351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222412</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>203927</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>242376</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>222431</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>202401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>240623</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>204381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>242149</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>222412</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>204029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>241746</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>418526</t>
+          <t>417681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>473440</t>
+          <t>471946</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2012 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2012 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67303</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57653</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78109</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65551</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55525</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75219</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55877</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75663</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>67303</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>57973</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78188</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119785</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147999</t>
+          <t>147189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>75145</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64339</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84795</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>76011</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66343</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86037</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65899</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85685</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75145</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64260</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84475</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136011</t>
+          <t>136821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164225</t>
+          <t>164032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,76%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>173541</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>160248</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>185548</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>144059</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>132031</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>156040</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>132240</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>155933</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>59,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>173541</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>159635</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>184969</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,01%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300926</t>
+          <t>300379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334526</t>
+          <t>334506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81615</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69608</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94908</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>77871</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65890</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89899</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>65997</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>89690</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>81615</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70187</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95521</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142560</t>
+          <t>142580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176160</t>
+          <t>176707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>255156</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>255156</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>255156</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>221930</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>221930</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>221930</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>255156</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>255156</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>255156</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110807</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100121</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119509</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107513</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98171</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116240</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>98248</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>116605</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>71,14%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110807</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>100789</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>118990</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204080</t>
+          <t>205002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>230434</t>
+          <t>231519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40375</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31673</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>51061</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43617</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34890</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52959</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34525</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>52882</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>28,86%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>40375</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32192</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50393</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71878</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98232</t>
+          <t>97310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>151182</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>151182</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>151182</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>151130</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>151130</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>151130</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>151182</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>151182</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>117190</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>106856</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125546</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>118556</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>109562</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>126732</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>108820</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>125889</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>77,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>117190</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>107669</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>126477</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222736</t>
+          <t>222399</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248921</t>
+          <t>247833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46257</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37901</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56591</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>34842</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26666</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43836</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>27509</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>44578</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>22,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>46257</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36970</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55778</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67923</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94108</t>
+          <t>94445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163447</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163447</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163447</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>153398</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>153398</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>153398</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163447</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163447</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>446719</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>489949</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>415593</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>454096</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>415703</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>455491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>446708</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>490247</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>874944</t>
+          <t>875273</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>933318</t>
+          <t>933404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>243392</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222283</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>265513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>232341</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>213923</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>252426</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>212528</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>252316</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>243392</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>221985</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>265524</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446933</t>
+          <t>446847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505307</t>
+          <t>504978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>712232</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>668019</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>712232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2016 (tasa de respuesta: 98,83%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2016 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42647</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34449</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51061</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47729</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39160</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56088</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39482</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56540</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42647</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>34091</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50490</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79249</t>
+          <t>78719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103290</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>75747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67333</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83945</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>79280</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70921</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87849</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>70469</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87527</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75747</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67904</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84303</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142113</t>
+          <t>141509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166154</t>
+          <t>166684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118394</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118394</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118394</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118394</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118394</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>159127</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>146811</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>170403</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>136722</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>126231</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>146448</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>126844</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>146967</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>70,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>159127</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145678</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>169789</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280622</t>
+          <t>279338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310777</t>
+          <t>310492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77737</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66461</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90053</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>58497</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48771</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>68988</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48252</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>68375</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>77737</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>67075</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>91186</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121306</t>
+          <t>121591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151461</t>
+          <t>152745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236864</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236864</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236864</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195219</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195219</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195219</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>236864</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>236864</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>236864</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>126089</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>116170</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>135324</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>121784</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>111695</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>130249</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>112196</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>131146</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>71,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>126089</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>116258</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135397</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>74,86%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234883</t>
+          <t>234485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260646</t>
+          <t>260844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42355</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33120</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52274</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>25,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>49454</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40989</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59543</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40092</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>59042</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>28,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>42355</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>33047</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79035</t>
+          <t>78837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104798</t>
+          <t>105196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168444</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168444</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168444</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>171238</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>171238</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>171238</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>168444</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168444</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>168444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>108129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>97943</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>116633</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>66,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>114922</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>105437</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>123021</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>105968</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>123510</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>74,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>68,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>108129</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>98593</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>117193</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>72,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208804</t>
+          <t>208879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235443</t>
+          <t>235115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40071</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31567</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50257</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>33,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>38888</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30789</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48373</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30300</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>47842</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40071</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>31007</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49607</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66567</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93206</t>
+          <t>93131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148200</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148200</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148200</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>153810</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>153810</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>153810</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148200</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148200</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148200</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>415725</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>456400</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>402102</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>441011</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>401981</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>440299</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>415971</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>454660</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>828723</t>
+          <t>829481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>884751</t>
+          <t>885929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>235909</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>215501</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>256176</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>226120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>206266</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>245175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>206978</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>245296</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>235909</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>217241</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>255930</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>434427</t>
+          <t>433249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>490455</t>
+          <t>489697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>974</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>647277</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>671901</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por diagnóstico y tratamiento en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por diagnóstico y/o tratamiento [en 2023 se preguntan por separado] en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7342</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9365</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6339</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12112</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>57,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6930</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9956</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23850</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19218</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23987</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19766</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26285</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51784</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46202</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4211</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8432</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29533</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24671</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32885</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24363</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27859</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>22313</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>25923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55153</t>
+          <t>51846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48457</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60443</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10892</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6933</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3437</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11272</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33340</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36985</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19620</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15703</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22788</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29373</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38175</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>53476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>58563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13526</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1738</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8823</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88848</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>103108</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69339</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>83614</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97109</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>157965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192659</t>
+          <t>178217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25279</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32874</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22981</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16700</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30975</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49980</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>39017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
